--- a/src/attributions/attributions_ig_traj_76.xlsx
+++ b/src/attributions/attributions_ig_traj_76.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG3"/>
+  <dimension ref="A1:GG16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,22 +999,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1312794072705492</v>
+        <v>0.2655584397055844</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2696233515299001</v>
+        <v>0.03065157554929767</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007675740627754522</v>
+        <v>-0.1320014248588164</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1023,31 +1023,31 @@
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.09162142013456404</v>
+        <v>0.1695723576314621</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2092013713451965</v>
+        <v>-0.2668367339331486</v>
       </c>
       <c r="N2" t="n">
-        <v>0.02010645451059558</v>
+        <v>-0.1713075144962301</v>
       </c>
       <c r="O2" t="n">
         <v>-0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>-0</v>
@@ -1056,16 +1056,16 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1042507738322135</v>
+        <v>0.08903089761303673</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.02676475543772707</v>
+        <v>-0.1258760389041352</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.006624392836992566</v>
+        <v>0.06365946714651118</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -1077,82 +1077,82 @@
         <v>-0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.01229826710515999</v>
+        <v>0.002175193676425076</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.01603021089254992</v>
+        <v>0.009239634745379274</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.002920549678736569</v>
+        <v>-0.01509309670729002</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI2" t="n">
         <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK2" t="n">
         <v>-0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.03213058706619464</v>
+        <v>0.1930412594731947</v>
       </c>
       <c r="AM2" t="n">
         <v>-0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.04866463345903858</v>
+        <v>-0.02802817584537037</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.05872192759438443</v>
+        <v>0.3383055206858002</v>
       </c>
       <c r="AP2" t="n">
         <v>-0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR2" t="n">
         <v>-0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.1420381477075912</v>
+        <v>0.4205406508250483</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.09604362001676886</v>
+        <v>0.005731532943881608</v>
       </c>
       <c r="AX2" t="n">
-        <v>-0.03007136911367418</v>
+        <v>-0.03550633696184125</v>
       </c>
       <c r="AY2" t="n">
         <v>-0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -1164,16 +1164,16 @@
         <v>-0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.01394801060804107</v>
+        <v>-0.02400256842970046</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.09774606981162738</v>
+        <v>0.06864323096943084</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.01691949969733672</v>
+        <v>-0.0165937304997036</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1188,55 +1188,55 @@
         <v>-0</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.01336856832920403</v>
+        <v>-0.1672025255906261</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0.03872286851754293</v>
+        <v>-0.1782432307923084</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.07789378838805426</v>
+        <v>-0.1016044509681614</v>
       </c>
       <c r="BQ2" t="n">
         <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU2" t="n">
         <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0.06541867347822705</v>
+        <v>0.237251970675172</v>
       </c>
       <c r="BW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.0286815084985256</v>
+        <v>-0.179053249679104</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.03667635841468975</v>
+        <v>0.02805521805299567</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC2" t="n">
         <v>0</v>
@@ -1245,19 +1245,19 @@
         <v>-0</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.03131965819972365</v>
+        <v>-0.2317745332444685</v>
       </c>
       <c r="CF2" t="n">
         <v>-0</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0.03792856407418337</v>
+        <v>-0.0083376679443663</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.01977921938127206</v>
+        <v>-0.03859280350988469</v>
       </c>
       <c r="CI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ2" t="n">
         <v>-0</v>
@@ -1266,58 +1266,58 @@
         <v>-0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.05526154718428198</v>
+        <v>-0.2118040322842316</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.04082519066560224</v>
+        <v>0.1916780870990179</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.07604816541436506</v>
+        <v>-0.2575455156967424</v>
       </c>
       <c r="CR2" t="n">
         <v>-0</v>
       </c>
       <c r="CS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU2" t="n">
         <v>-0</v>
       </c>
       <c r="CV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.04869620284243264</v>
+        <v>-0.2399402906861352</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>-0.04133256821757724</v>
+        <v>-0.001747245239860765</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.01431381162547751</v>
+        <v>0.01576642851591265</v>
       </c>
       <c r="DA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB2" t="n">
         <v>-0</v>
       </c>
       <c r="DC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD2" t="n">
         <v>0</v>
@@ -1326,25 +1326,25 @@
         <v>-0</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.04211323188845133</v>
+        <v>-0.09433526416230371</v>
       </c>
       <c r="DG2" t="n">
         <v>-0</v>
       </c>
       <c r="DH2" t="n">
-        <v>-0.005094718869252873</v>
+        <v>0.1248086008200805</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.009147846176215805</v>
+        <v>0.02026451108830548</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK2" t="n">
         <v>-0</v>
       </c>
       <c r="DL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM2" t="n">
         <v>-0</v>
@@ -1353,19 +1353,19 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.01458424503963165</v>
+        <v>-0.154858056813519</v>
       </c>
       <c r="DP2" t="n">
         <v>0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.06318707184845157</v>
+        <v>0.2042260528145992</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.01288648389114542</v>
+        <v>-0.01166542942608386</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT2" t="n">
         <v>0</v>
@@ -1377,28 +1377,28 @@
         <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.05106129249218446</v>
+        <v>-0.07735689398285532</v>
       </c>
       <c r="DY2" t="n">
         <v>-0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.002891590206178732</v>
+        <v>0.3301619760459391</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.02682700005420498</v>
+        <v>0.2686739602847398</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
         <v>-0</v>
       </c>
       <c r="ED2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE2" t="n">
         <v>-0</v>
@@ -1407,19 +1407,19 @@
         <v>-0</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.03505717613743062</v>
+        <v>-0.2323113017117388</v>
       </c>
       <c r="EH2" t="n">
         <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.09774273743666885</v>
+        <v>0.406505541412253</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.01855732252884039</v>
+        <v>0.05927932546553253</v>
       </c>
       <c r="EK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL2" t="n">
         <v>0</v>
@@ -1431,25 +1431,25 @@
         <v>0</v>
       </c>
       <c r="EO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.06391125286757442</v>
+        <v>-0.122244066697624</v>
       </c>
       <c r="EQ2" t="n">
         <v>0</v>
       </c>
       <c r="ER2" t="n">
-        <v>-0.05342716592926169</v>
+        <v>0.05410813734811391</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.01560759277549106</v>
+        <v>0.02763184372413201</v>
       </c>
       <c r="ET2" t="n">
         <v>0</v>
       </c>
       <c r="EU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV2" t="n">
         <v>0</v>
@@ -1458,22 +1458,22 @@
         <v>0</v>
       </c>
       <c r="EX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.03939709954443905</v>
+        <v>-0.2838598321129182</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>-0.0334448179641134</v>
+        <v>0.03601436680847005</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.02489131420894644</v>
+        <v>0.004959032916063433</v>
       </c>
       <c r="FC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD2" t="n">
         <v>-0</v>
@@ -1488,16 +1488,16 @@
         <v>-0</v>
       </c>
       <c r="FH2" t="n">
-        <v>-0.002947118385050842</v>
+        <v>-0.2143296291375973</v>
       </c>
       <c r="FI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>-0.03186331621889533</v>
+        <v>-0.129164534685147</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.01550483445938226</v>
+        <v>0.07479071477653804</v>
       </c>
       <c r="FL2" t="n">
         <v>-0</v>
@@ -1506,52 +1506,52 @@
         <v>0</v>
       </c>
       <c r="FN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO2" t="n">
         <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.001061672145293953</v>
+        <v>-0.1825649159441348</v>
       </c>
       <c r="FR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.01328256027017473</v>
+        <v>0.3743512248655848</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.002496242915856067</v>
+        <v>-0.07703430507866213</v>
       </c>
       <c r="FU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW2" t="n">
         <v>-0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY2" t="n">
         <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.03271345762496612</v>
+        <v>-0.1038111571183357</v>
       </c>
       <c r="GA2" t="n">
         <v>0</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.02005732247023465</v>
+        <v>0.02682704077200624</v>
       </c>
       <c r="GC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD2" t="n">
         <v>0</v>
@@ -1568,106 +1568,106 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>-0.001734479376096567</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0.004908952487787143</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0.004879103434077505</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-0.003579760809182949</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>-0.005275424206182068</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0.001031667945518737</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.01877180660338651</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0</v>
+        <v>0.01137459314338402</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0.01183600106561576</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>-0.002427555358888286</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0</v>
+        <v>-0.001219388470012863</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>-0.004753161566814453</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1676,106 +1676,106 @@
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>0.005715681617269783</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0</v>
+        <v>0.01077997979768519</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>0.002200389238596411</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>0.01355011217710353</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0</v>
+        <v>0.02433067380472168</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>-0.009537938950931576</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>-0.0045064654577919</v>
       </c>
       <c r="BD3" t="n">
         <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF3" t="n">
         <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0</v>
+        <v>-0.005749122748996067</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>0.0007783037458039449</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK3" t="n">
         <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>0.002945880895220567</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0</v>
+        <v>0.01200269169395263</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>-0.002254788087575399</v>
       </c>
       <c r="BS3" t="n">
         <v>0</v>
@@ -1784,52 +1784,52 @@
         <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>0.01582489877491211</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
         <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0</v>
+        <v>0.01656020619508253</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>-0.01111251721392699</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC3" t="n">
         <v>0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0</v>
+        <v>0.0004230950069604557</v>
       </c>
       <c r="CE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CF3" t="n">
         <v>0</v>
       </c>
       <c r="CG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0</v>
+        <v>-0.008182283361606205</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>0.003916190485275788</v>
       </c>
       <c r="CK3" t="n">
         <v>0</v>
@@ -1838,7 +1838,7 @@
         <v>0</v>
       </c>
       <c r="CM3" t="n">
-        <v>0</v>
+        <v>-0.0005916350164618049</v>
       </c>
       <c r="CN3" t="n">
         <v>0</v>
@@ -1847,97 +1847,97 @@
         <v>0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0</v>
+        <v>-0.03404912217405446</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>0.01444090103666112</v>
       </c>
       <c r="CT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV3" t="n">
-        <v>0</v>
+        <v>0.002810942648519179</v>
       </c>
       <c r="CW3" t="n">
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY3" t="n">
         <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0</v>
+        <v>-0.01118392770585648</v>
       </c>
       <c r="DA3" t="n">
         <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>0.006862616814878082</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>0.0007235166489462164</v>
       </c>
       <c r="DF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DG3" t="n">
         <v>0</v>
       </c>
       <c r="DH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0</v>
+        <v>-0.01318963295851677</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>0.003911967265814048</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN3" t="n">
-        <v>0</v>
+        <v>0.01035220977340342</v>
       </c>
       <c r="DO3" t="n">
         <v>0</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0</v>
+        <v>-0.02283651488719002</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>0.003348726166250255</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
@@ -1946,34 +1946,34 @@
         <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>0.006903299885854806</v>
       </c>
       <c r="DX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0</v>
+        <v>0.001215788426309717</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC3" t="n">
-        <v>0</v>
+        <v>0.02223013293366028</v>
       </c>
       <c r="ED3" t="n">
         <v>0</v>
       </c>
       <c r="EE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF3" t="n">
-        <v>0</v>
+        <v>0.005413296795195148</v>
       </c>
       <c r="EG3" t="n">
         <v>0</v>
@@ -1982,16 +1982,16 @@
         <v>0</v>
       </c>
       <c r="EI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0</v>
+        <v>-0.007968729421212422</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>-0.0001287144460115185</v>
       </c>
       <c r="EM3" t="n">
         <v>0</v>
@@ -2000,61 +2000,61 @@
         <v>0</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>-0.00408671368442466</v>
       </c>
       <c r="EP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EQ3" t="n">
         <v>0</v>
       </c>
       <c r="ER3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0</v>
+        <v>-0.01697911504187248</v>
       </c>
       <c r="ET3" t="n">
         <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>0.004651338828292213</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW3" t="n">
         <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>0.002962678941688894</v>
       </c>
       <c r="EY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ3" t="n">
         <v>0</v>
       </c>
       <c r="FA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0</v>
+        <v>-0.01581604174403687</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>0.009984084873996461</v>
       </c>
       <c r="FE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF3" t="n">
         <v>0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0</v>
+        <v>0.004018138466752185</v>
       </c>
       <c r="FH3" t="n">
         <v>0</v>
@@ -2063,25 +2063,25 @@
         <v>0</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0</v>
+        <v>0.01688803765164931</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM3" t="n">
-        <v>0</v>
+        <v>-0.006685803621576066</v>
       </c>
       <c r="FN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO3" t="n">
         <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>-0.02297079401828475</v>
       </c>
       <c r="FQ3" t="n">
         <v>0</v>
@@ -2093,45 +2093,7442 @@
         <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0</v>
+        <v>0.004149145320166336</v>
       </c>
       <c r="FU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV3" t="n">
-        <v>0</v>
+        <v>-0.005256625562690899</v>
       </c>
       <c r="FW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>-0.00431861038932081</v>
       </c>
       <c r="FZ3" t="n">
         <v>0</v>
       </c>
       <c r="GA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>0.01468393990616244</v>
       </c>
       <c r="GF3" t="n">
         <v>0</v>
       </c>
       <c r="GG3" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-0.3672281954257873</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.05782176959463108</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1379890620043527</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.3815769513631757</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.1165721073427891</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.03953917561620047</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.06647665567070611</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.05744142802972719</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.09043395056330347</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-0.02737540647571966</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.01046732984069727</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-0.02620230171189077</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-0.1790634194283194</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-0.1619359640240951</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.08171650745551112</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>-0.5772531438671975</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.1501396258851143</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.1766249090735413</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.0069020762337935</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>-0.0002059056141530914</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0.01229010878968432</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.09271483698807742</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>-0.06975684627854262</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>-0.03179783210981831</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>-0.4565806932386343</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>0.03080035993100637</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0.1896641406372759</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0.3194881777999031</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>-0.01247715975938855</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>-0.1064796637213495</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>0.3274149596842409</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>-0.005388823080116303</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>-0.1631238659395215</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>0.3174819550062231</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>-0.02004953729255361</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>-0.1068961419755319</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>0.04611486838660527</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>0.02637858718181342</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>-0.08600172586884501</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>0.1773487174558162</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>0.01462884051034543</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>0.01845995430646016</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>-0.1389007821215093</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>0.02555773813105318</v>
+      </c>
+      <c r="EB4" t="n">
+        <v>0.1943735646705376</v>
+      </c>
+      <c r="EC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG4" t="n">
+        <v>0.2202623492056055</v>
+      </c>
+      <c r="EH4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ4" t="n">
+        <v>-0.01484599151788532</v>
+      </c>
+      <c r="EK4" t="n">
+        <v>-0.04761321187396528</v>
+      </c>
+      <c r="EL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP4" t="n">
+        <v>0.1885901706610389</v>
+      </c>
+      <c r="EQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES4" t="n">
+        <v>-0.03860225662467827</v>
+      </c>
+      <c r="ET4" t="n">
+        <v>-0.04884647594755674</v>
+      </c>
+      <c r="EU4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY4" t="n">
+        <v>0.338655864400586</v>
+      </c>
+      <c r="EZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB4" t="n">
+        <v>-0.002984770196333863</v>
+      </c>
+      <c r="FC4" t="n">
+        <v>-0.1002777498181229</v>
+      </c>
+      <c r="FD4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH4" t="n">
+        <v>0.1286902272703376</v>
+      </c>
+      <c r="FI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK4" t="n">
+        <v>0.09083433476808798</v>
+      </c>
+      <c r="FL4" t="n">
+        <v>-0.07263903040349143</v>
+      </c>
+      <c r="FM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ4" t="n">
+        <v>0.3272122252116875</v>
+      </c>
+      <c r="FR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT4" t="n">
+        <v>0.03397679622661876</v>
+      </c>
+      <c r="FU4" t="n">
+        <v>-0.1332968599581463</v>
+      </c>
+      <c r="FV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ4" t="n">
+        <v>0.1944924462798684</v>
+      </c>
+      <c r="GA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD4" t="n">
+        <v>-0.04361676134515116</v>
+      </c>
+      <c r="GE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG4" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.004520810232377478</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.02548314827560257</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.01283795916378306</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.006146913424522008</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.03688985736917118</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.01227797182954469</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.01109103804773905</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.01178918039169698</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.01057206912125877</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-0.001355318115077987</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-0.002520430065480092</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-0.0003447530757852113</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.006078523213300863</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-0.01265700321741618</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-0.0001083229509625671</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.02729557540657268</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0.04684795350312369</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>-0.00620302883246076</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>-0.01956274004559236</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>-0.00212620225668889</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>-0.002245179851117667</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0.01299052914531353</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0.007868578752409311</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0.01267169676638043</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>0.01013050729158455</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0.02032563496995889</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>-0.007656897528785752</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0.001128244798178944</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>-0.009496039924143031</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0.01286758529121263</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>-0.001027740648363821</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>0.01349158175976765</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>0.01217003749153979</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>0.002351188347914198</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>-0.01202174226674178</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>0.01345875006353845</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>-0.005293118517854714</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>-0.0007706738921869045</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0.005536445809306426</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>0.004670895090142143</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>-0.01739657071282</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>-0.0005674066097984121</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>-0.001512852655811196</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>-0.02010106378973262</v>
+      </c>
+      <c r="EC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED5" t="n">
+        <v>-0.009067261762648068</v>
+      </c>
+      <c r="EE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ5" t="n">
+        <v>0.006177490664917793</v>
+      </c>
+      <c r="EK5" t="n">
+        <v>-0.01291406523696439</v>
+      </c>
+      <c r="EL5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM5" t="n">
+        <v>0.007097141036996371</v>
+      </c>
+      <c r="EN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES5" t="n">
+        <v>-0.009085443237658818</v>
+      </c>
+      <c r="ET5" t="n">
+        <v>-0.01665730369912484</v>
+      </c>
+      <c r="EU5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV5" t="n">
+        <v>0.01199109294478222</v>
+      </c>
+      <c r="EW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB5" t="n">
+        <v>-0.0003746537158518106</v>
+      </c>
+      <c r="FC5" t="n">
+        <v>-0.01008873176845558</v>
+      </c>
+      <c r="FD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE5" t="n">
+        <v>0.01385514013284658</v>
+      </c>
+      <c r="FF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK5" t="n">
+        <v>-0.003390912954019029</v>
+      </c>
+      <c r="FL5" t="n">
+        <v>0.004167799991319499</v>
+      </c>
+      <c r="FM5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN5" t="n">
+        <v>0.01558107486955136</v>
+      </c>
+      <c r="FO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT5" t="n">
+        <v>-0.02973279763314739</v>
+      </c>
+      <c r="FU5" t="n">
+        <v>-0.05102276337352279</v>
+      </c>
+      <c r="FV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW5" t="n">
+        <v>0.004909559619461291</v>
+      </c>
+      <c r="FX5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GA5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD5" t="n">
+        <v>-0.01529689540693373</v>
+      </c>
+      <c r="GE5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF5" t="n">
+        <v>0.005791714289861958</v>
+      </c>
+      <c r="GG5" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.03501925634010804</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.01800375358518042</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.03933341877379692</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.0255490698140824</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.01287628394532755</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.03860446815715828</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.004592362066178358</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.02382342674545925</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.002789831478353648</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-0.01071754885748343</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-0.01553131202261122</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0.01466183360561034</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-0.03609536792323536</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.01732629523099783</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1.996311246048476e-05</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-0.06503289643253408</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.09379113467420325</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-0.0851697762059337</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.0004219633238163101</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-0.04820562743654833</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-0.02146107917417338</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0.01678523395424397</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0.04820706091519253</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.06773018991386742</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>-0.03312656500566592</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0.09524523051610673</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>-0.01441678493851113</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0.02625963520467488</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.006824115766720362</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.009419751572682402</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>0.0131731937785592</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>0.02198228834203504</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>0.06081173873206057</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>0.01820116089241361</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>0.003998708282726592</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>0.02039345318727289</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0.01170943007901689</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>-0.02114500349162779</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>-0.002043092007074436</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>0.008465635657623887</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>-0.007556972077097038</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>0.04192039288441478</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>-0.03293338305683217</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>-0.01947363234344802</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>-0.03229592638590866</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>-0.002424352845907031</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>0.01488652497050834</v>
+      </c>
+      <c r="EJ6" t="n">
+        <v>-0.003055838880456945</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ6" t="n">
+        <v>-0.005091996649096789</v>
+      </c>
+      <c r="ER6" t="n">
+        <v>-0.02007039546526832</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>0.01218194936965704</v>
+      </c>
+      <c r="ET6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ6" t="n">
+        <v>0.01884920957254008</v>
+      </c>
+      <c r="FA6" t="n">
+        <v>-0.004700499520995619</v>
+      </c>
+      <c r="FB6" t="n">
+        <v>0.01411821091277532</v>
+      </c>
+      <c r="FC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI6" t="n">
+        <v>0.01661168966920384</v>
+      </c>
+      <c r="FJ6" t="n">
+        <v>-0.002685157621702132</v>
+      </c>
+      <c r="FK6" t="n">
+        <v>-0.04238382091309489</v>
+      </c>
+      <c r="FL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR6" t="n">
+        <v>3.934788834994866e-05</v>
+      </c>
+      <c r="FS6" t="n">
+        <v>0.003392978466042412</v>
+      </c>
+      <c r="FT6" t="n">
+        <v>0.05132137987282395</v>
+      </c>
+      <c r="FU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA6" t="n">
+        <v>0.01155073262297827</v>
+      </c>
+      <c r="GB6" t="n">
+        <v>-0.02927161626445916</v>
+      </c>
+      <c r="GC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG6" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.2503941783463266</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.04354074010111095</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.1082474882554239</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.3529543536091608</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0.008069257480609621</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-0.1182442737698028</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.08839682388704319</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0.09721137553492774</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.02336715599341926</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-0.0118336027358107</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0.08014546506662854</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-0.02134443458232521</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.05366361774645988</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-0.01138303085387012</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-0.05286937764898148</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.3857018776480945</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-0.1736593883816442</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>-0.06661615531932497</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-0.01736416592631222</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-0.01735183111911656</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>-0.06638808952646492</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.06858799061032202</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0.0614838581771348</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0.01099700222375083</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0.2701075878710738</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>-0.05799450624704959</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>-0.07283926933109415</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>-0.09923716279639741</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>-0.01498331795866485</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0.05404509138461135</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>-0.1747925475302224</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>0.1150243244126416</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>0.05594853271690287</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>-0.08837129970834574</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>-0.03497729795452542</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0.05743884439276268</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>-0.03663484482384912</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>-0.07954117362766847</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>-0.01404486022950918</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>-0.05061302566384042</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>-0.04650249378280968</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0.003428958390357815</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>0.05706588383190388</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>-0.01058164990318528</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>0.01933904310505061</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>-0.002541899292217534</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>-0.07562148745632045</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>0.01860685305002844</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP8" t="n">
+        <v>-0.01111399727417037</v>
+      </c>
+      <c r="EQ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES8" t="n">
+        <v>-0.09730490982256185</v>
+      </c>
+      <c r="ET8" t="n">
+        <v>0.04131880369840913</v>
+      </c>
+      <c r="EU8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY8" t="n">
+        <v>-0.110715121525507</v>
+      </c>
+      <c r="EZ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB8" t="n">
+        <v>-0.03415898260129065</v>
+      </c>
+      <c r="FC8" t="n">
+        <v>0.04255460666031068</v>
+      </c>
+      <c r="FD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH8" t="n">
+        <v>-0.09915570728337468</v>
+      </c>
+      <c r="FI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK8" t="n">
+        <v>0.09073672026253761</v>
+      </c>
+      <c r="FL8" t="n">
+        <v>0.0678533348717113</v>
+      </c>
+      <c r="FM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ8" t="n">
+        <v>0.02568119386667738</v>
+      </c>
+      <c r="FR8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT8" t="n">
+        <v>-0.02385849125205413</v>
+      </c>
+      <c r="FU8" t="n">
+        <v>0.025872845560229</v>
+      </c>
+      <c r="FV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ8" t="n">
+        <v>-0.06237675215901579</v>
+      </c>
+      <c r="GA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD8" t="n">
+        <v>0.01493994779915329</v>
+      </c>
+      <c r="GE8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.3479741288887487</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.1696448212608979</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.007422733024831339</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.402055872110907</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.2198310073558277</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.03295056527008668</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.09418859851524387</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0.03505591052191264</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.07800744392685759</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-0.06028107700541258</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-0.07324541058189296</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-0.04094677599192958</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.1032492630757987</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-0.05072342811745973</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.04955113812210116</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.3370938859734188</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>-0.09211114922261067</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>-0.1304331652270187</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>-0.01821697253695006</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>-0.04325061148896341</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>-0.0107015151090394</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>-0.03994509482066016</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0.005149826395470168</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.03345999405097997</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.2940625187048709</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>-0.1195943234820088</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>-0.04088904000097972</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>-0.129709417096469</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.1203124933383748</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>-0.0170826617649228</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>-0.1127362921866758</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.2140268737609498</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0.0482084108439672</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>-0.1212948017396682</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0.1228461948194744</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>-0.006898683844696632</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>-0.08334857864803505</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0.01558245625648095</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>-0.05801086446657901</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>-0.07533902880545749</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0.09382575748529619</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>-0.01266955700555564</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0.02600821269405029</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>-0.05629514531041691</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>0.04226624076027799</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>-0.08740562310917169</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>0.07117836963366761</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>0.01452364106939523</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>-0.06306510257113387</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>0.04691124939377768</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>-0.02642548816736122</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>-0.1383018233718567</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA9" t="n">
+        <v>0.1262469586144748</v>
+      </c>
+      <c r="FB9" t="n">
+        <v>-0.01930401991991051</v>
+      </c>
+      <c r="FC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH9" t="n">
+        <v>-0.09609457480039875</v>
+      </c>
+      <c r="FI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ9" t="n">
+        <v>0.07588584510139673</v>
+      </c>
+      <c r="FK9" t="n">
+        <v>-0.004855250358317891</v>
+      </c>
+      <c r="FL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ9" t="n">
+        <v>0.00496066672948477</v>
+      </c>
+      <c r="FR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS9" t="n">
+        <v>0.05097066510454915</v>
+      </c>
+      <c r="FT9" t="n">
+        <v>-0.01054324346865373</v>
+      </c>
+      <c r="FU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ9" t="n">
+        <v>-0.1191297257632182</v>
+      </c>
+      <c r="GA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB9" t="n">
+        <v>0.04151415424333329</v>
+      </c>
+      <c r="GC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.4585156283807222</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.017803152729276</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.1934048132633278</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.6760396497274647</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.131131640763072</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.1562791827801858</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.129402378178797</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.1113113747369525</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.004805710563117789</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.01380806060982256</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-0.1969741150277859</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-0.06924236680279409</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.04738332400103701</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.01147077114292095</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-0.04244574032354768</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.6785642411309663</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-0.1414319694150896</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>-0.1608204652823647</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.002726853764090446</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>-0.07659094833524804</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>-0.07705915096134996</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.07497139413660846</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0.1019312907940263</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>-0.05988317586853546</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0.4519340911281906</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>-0.04571321343998968</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>-0.07940403395075053</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>-0.1827779906920406</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0.01526849907402072</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0.08031662235358082</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>-0.2782196660394707</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>0.1205935694412272</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>0.1324836040769823</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>-0.183789891767765</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>-0.01448517541150976</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>0.08654838746075456</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>-0.08893300328464591</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>-0.1941716769481718</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>0.04349208725620927</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>-0.1319078677640293</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>0.08058976519930716</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>-0.0277909086843878</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>0.02782131457889257</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>0.1555887609887391</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>-0.1865154923072042</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>-0.04851265534637463</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>-0.06417001863241872</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>0.03379276564995148</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>-0.02866655438910596</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>-0.08580042112478625</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>0.08381624078880358</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>-0.2128780168274191</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>-0.02453261173842101</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>0.08215829782674254</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>-0.2213581819220997</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>0.1431227694421806</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>0.006785746712163418</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>0.001840131431580369</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>-0.004293064496396348</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>-0.01434648382844791</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>-0.06469756238551164</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>-0.006661383506028275</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.5537066628059077</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.3113461477554801</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.0923626771005155</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.6503987366762102</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.4131580725723147</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.1519601156630545</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.1365111791536264</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0.1309927057132179</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.1524698074286496</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-0.04921883545896785</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-0.1349103405823947</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-0.1573223393736481</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.1037205708822368</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-0.09351935179733821</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.03497916561340224</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.7241939572633517</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>-0.1900294720474773</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>-0.2782014623168343</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>-0.09204054625460914</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-0.06588148475902722</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>-0.08886693620304909</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.005169818089102534</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0.009424616635372243</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0.1046276484693692</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0.4820340769416118</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>-0.2394322821155811</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>-0.1022653702379997</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>-0.2287650268043945</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0.1628176951521411</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0.04475083829137758</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>-0.2272582348798993</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0.3645794225540485</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>0.117206162534893</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>-0.2137720258757046</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>0.1824141781417336</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>0.02633576488131517</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>-0.1292263528009031</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0.02803315745904648</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>-0.1428924826371614</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>-0.09993567169888738</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>-0.01556750108216737</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>-0.03962910438119669</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>0.1462723638982408</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>0.1228797205278899</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>-0.02076089230316922</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>-0.1460348283372752</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>0.1009971404896869</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>0.0895168236390235</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>-0.06509837828643462</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>0.1407589684668473</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>-0.06505001326643944</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>-0.2556094087551904</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>0.1946037135845684</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>0.01750903859788535</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>-0.1310025082598958</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>0.1102593197194506</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>0.01829245733350324</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>0.001181681537579309</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>0.2135141040684968</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>-0.006222504701551794</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>-0.1889963071045989</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>0.1444192899397705</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-0.4371235012767976</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.02406830723707033</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.4306677231023531</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.4970474072324269</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.1382938992233796</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.4238764437378133</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-0.1833521224445047</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.1716146720911706</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.0578933333813112</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-0.0158388799003307</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.2807256547594891</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.1546807462915067</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>-0.1669657591069283</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-0.06652167719734962</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0.137518290822297</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>-0.8676116674337339</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0.07721350912427842</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0.274373848509149</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0.1703983050877648</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0.2612548744277752</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0.1757985399891939</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>-0.07529190478810792</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>-0.1719132362575122</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>-0.01457864078032096</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>-0.3837165099620769</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>0.08989714627985901</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>0.2823096998672862</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>0.188398209281701</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>-0.03385258400417801</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>-0.1558954347103353</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>0.3487843099324474</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>-0.2384427660662415</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>-0.216629179114519</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>0.1731235922617229</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>-0.01256282333131307</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>-0.1528969327979298</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>0.02725620609333407</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>0.1943455822641778</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>-0.009005871846760979</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>0.09724036368842535</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>-0.05303411303182699</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>-0.02776540769686243</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>-0.07974366813084312</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>0.02728688838651624</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>-0.07760341498347077</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>0.03961638279629112</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>0.08125136386751747</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>-0.02548277861087456</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>0.05603393684170243</v>
+      </c>
+      <c r="EQ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER12" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES12" t="n">
+        <v>0.09963998135613286</v>
+      </c>
+      <c r="ET12" t="n">
+        <v>-0.1003916408041556</v>
+      </c>
+      <c r="EU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY12" t="n">
+        <v>0.2046316022898013</v>
+      </c>
+      <c r="EZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB12" t="n">
+        <v>0.009162277995748105</v>
+      </c>
+      <c r="FC12" t="n">
+        <v>-0.1418849144682578</v>
+      </c>
+      <c r="FD12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH12" t="n">
+        <v>0.2277434220959422</v>
+      </c>
+      <c r="FI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK12" t="n">
+        <v>-0.05693302263670699</v>
+      </c>
+      <c r="FL12" t="n">
+        <v>0.236455937564275</v>
+      </c>
+      <c r="FM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ12" t="n">
+        <v>0.0586318007818978</v>
+      </c>
+      <c r="FR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT12" t="n">
+        <v>0.0001984320679915498</v>
+      </c>
+      <c r="FU12" t="n">
+        <v>-0.2026361238353598</v>
+      </c>
+      <c r="FV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ12" t="n">
+        <v>0.08090237683713537</v>
+      </c>
+      <c r="GA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD12" t="n">
+        <v>0.04353505953097326</v>
+      </c>
+      <c r="GE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG12" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.3807820340654174</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.2166479685224378</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.02007161171591568</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.4473875402622344</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-0.3062861523254922</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-0.03068389123140634</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.07869695684674488</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-0.01279102809863453</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.07465366819173219</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.01278376918761865</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-0.1520031360495961</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.002327987784743708</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.06645953486357144</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-0.02139946459225725</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.01403581705347425</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.3210454171555405</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>-0.1363902410142125</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>-0.2327632974733389</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0.02138835128388342</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-0.1027317160026049</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.05820320194190012</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.005022245023769021</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0.0139936136326582</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0.06318197040361669</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0.2206748959362733</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>-0.07823107685749912</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>-0.05453925343409906</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>-0.1114502659063819</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0.1133101793382598</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>-0.01806941047266914</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>-0.1065199178747483</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>0.2188033307139344</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>0.02148898570983873</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>-0.0996666408760883</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>0.1221363595651216</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>-0.01694012108829439</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>-0.06085233060121768</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>0.06651746498230642</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>-0.11759905433696</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>-0.08853451104429802</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>0.06229906027689888</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>-0.05470485032011335</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>-0.009622544868604855</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>0.03135301319073351</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>-0.04498946350094256</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>-0.05970403657173984</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>-0.1493788905232494</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>-0.000938839984379442</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>-0.03631177220413784</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>0.007382017311736983</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>-0.008249043636606744</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>-0.129525931582738</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA13" t="n">
+        <v>0.137592608166012</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>-0.02163514356195747</v>
+      </c>
+      <c r="FC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH13" t="n">
+        <v>0.1039702661337421</v>
+      </c>
+      <c r="FI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ13" t="n">
+        <v>0.1027798161950255</v>
+      </c>
+      <c r="FK13" t="n">
+        <v>-0.0174826823846701</v>
+      </c>
+      <c r="FL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ13" t="n">
+        <v>-0.1399923383578674</v>
+      </c>
+      <c r="FR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS13" t="n">
+        <v>0.1531073321864995</v>
+      </c>
+      <c r="FT13" t="n">
+        <v>0.1861776906465886</v>
+      </c>
+      <c r="FU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ13" t="n">
+        <v>-0.08127289807776153</v>
+      </c>
+      <c r="GA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB13" t="n">
+        <v>0.0435281503489037</v>
+      </c>
+      <c r="GC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.05745599301583969</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.02590105445308199</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.0112972159680771</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.01066196075769661</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0735930183929842</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-0.02847828199191605</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.01084505550691432</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.01951156469030927</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.01589166105053721</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.0135990355748754</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.0001266281378650464</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.001400895438430193</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.01041331561347701</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0.008624261698537368</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.01689549369844816</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-0.01200551347666687</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.01256675353500063</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-0.002314740945130653</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.01507825910887135</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-0.001436946400744978</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.05474654998758541</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.004110785839688999</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0.002849001121785768</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.001951834748664035</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>-0.008205966054106317</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>-0.02189973047129874</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>-0.01113204251499955</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-0.003571505361928833</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.001225130292445639</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0.003084474661151424</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0.01362437251510696</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>-0.003103863388017901</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0.03656278799798156</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0.007611094177827162</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>0.004107768333408052</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>9.989758170983501e-05</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>-0.01861200595439398</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>0.008119027513747787</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>-0.0020721209313867</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0.005226449569253167</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>-0.02172582499881515</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>0.003519176254257037</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>0.01181232477103921</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>-0.004250211249512125</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>-0.01945559927809472</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>0.007371895705223045</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>-0.002468733617308145</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>0.006865930737869303</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>-0.002860137173110163</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>0.01488465688681556</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>-0.03979473952379899</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>0.01199799611243325</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>-0.008776076508668006</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>-6.793050063084797e-05</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>-0.009437012027808063</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>0.006490892045839106</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>-0.02244463841185462</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>-4.403199705817956e-05</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>0.00247428768261656</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>-0.02048388370197648</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>-0.008441536777363194</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>0.003533661049596536</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>0.002207337432006904</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>-0.0002448950276274382</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP14" t="n">
+        <v>-0.008533557126157753</v>
+      </c>
+      <c r="EQ14" t="n">
+        <v>0.001909824818183563</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>0.005299179517855515</v>
+      </c>
+      <c r="ET14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU14" t="n">
+        <v>0.0006711035245595779</v>
+      </c>
+      <c r="EV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY14" t="n">
+        <v>-0.02280699265463884</v>
+      </c>
+      <c r="EZ14" t="n">
+        <v>0.006209481599814425</v>
+      </c>
+      <c r="FA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB14" t="n">
+        <v>-0.002809870182389821</v>
+      </c>
+      <c r="FC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD14" t="n">
+        <v>0.004646773800656188</v>
+      </c>
+      <c r="FE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH14" t="n">
+        <v>0.00744946017355361</v>
+      </c>
+      <c r="FI14" t="n">
+        <v>0.0123539241673098</v>
+      </c>
+      <c r="FJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK14" t="n">
+        <v>0.01597884408655009</v>
+      </c>
+      <c r="FL14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM14" t="n">
+        <v>-0.01088224271086708</v>
+      </c>
+      <c r="FN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ14" t="n">
+        <v>-0.01551417556859531</v>
+      </c>
+      <c r="FR14" t="n">
+        <v>-0.01077427603043528</v>
+      </c>
+      <c r="FS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT14" t="n">
+        <v>0.01897746818861833</v>
+      </c>
+      <c r="FU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FV14" t="n">
+        <v>0.002178207851813701</v>
+      </c>
+      <c r="FW14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ14" t="n">
+        <v>-0.02301280348783624</v>
+      </c>
+      <c r="GA14" t="n">
+        <v>-0.001161001891423945</v>
+      </c>
+      <c r="GB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE14" t="n">
+        <v>-0.003977507845417367</v>
+      </c>
+      <c r="GF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.5649541793306214</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.0518395392227451</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.3580925591703785</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.7361786698378121</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.04057470249584846</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.5174631300721676</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.1877041745446287</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.09562567772941262</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.1374899761708116</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.01696368162247134</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0.3536527136521438</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>-0.01867562931029375</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.1395487148108705</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-0.02745115041707313</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-0.0923696882900155</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0.9867073690744402</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-0.3110455220739778</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>-0.4353066529618462</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>-0.1900642321771885</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>-0.03981455944538928</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0.04475565787948887</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.203735501876187</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0.1205295419064986</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>-0.03536935871282771</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0.4883827610786289</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>-0.07704506397963284</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>-0.2842484709845898</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>-0.2097487506088369</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0.05739987348089028</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0.09289972855996258</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>-0.3816493044427596</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>0.2528874134257927</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>0.1162193615301228</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>-0.1946429791491124</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>0.002203060703730397</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>0.128581418956033</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>-0.08290390003201333</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>-0.1964315992440358</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>0.03519065800207725</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>-0.07495130854173999</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>0.04401229807229912</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>0.1553008671253669</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>-0.1833137485047188</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>-0.08211147931993908</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>-0.02312522333280378</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>-0.02383379932494959</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>-0.0347044476168711</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>-0.04823617862177482</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>-0.1088431651110142</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>-0.02525892889258948</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>0.04316413867920667</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>-0.2357631999511348</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB15" t="n">
+        <v>-0.004016884647356769</v>
+      </c>
+      <c r="FC15" t="n">
+        <v>0.1121515531277381</v>
+      </c>
+      <c r="FD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH15" t="n">
+        <v>0.09213532179542021</v>
+      </c>
+      <c r="FI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK15" t="n">
+        <v>-0.01166517028949099</v>
+      </c>
+      <c r="FL15" t="n">
+        <v>0.2464454612475002</v>
+      </c>
+      <c r="FM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ15" t="n">
+        <v>-0.1183201383233434</v>
+      </c>
+      <c r="FR15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT15" t="n">
+        <v>0.3131015104153096</v>
+      </c>
+      <c r="FU15" t="n">
+        <v>-0.05094644359943281</v>
+      </c>
+      <c r="FV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ15" t="n">
+        <v>-0.05879193227909165</v>
+      </c>
+      <c r="GA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD15" t="n">
+        <v>0.11556667679125</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG16" t="n">
         <v>0</v>
       </c>
     </row>
